--- a/V5.0_双人执行工作区/00_共享/模型交接/RELATIONSHIP_MAP_V50.xlsx
+++ b/V5.0_双人执行工作区/00_共享/模型交接/RELATIONSHIP_MAP_V50.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R25d67976c79645d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关系图" sheetId="2" r:id="Re958007e9a0748a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="禁止关系" sheetId="3" r:id="R5fea16db2f894df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模顺序" sheetId="4" r:id="R4dc05b5a2cc8417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9f51462de65947f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关系图" sheetId="2" r:id="Rb77ec9ca04dc49d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="禁止关系" sheetId="3" r:id="R98f8318e65b849e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模顺序" sheetId="4" r:id="Rafb3934078074188"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -154,7 +154,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -165,7 +165,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -176,7 +176,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -187,7 +187,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -198,7 +198,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -209,7 +209,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -220,7 +220,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -231,7 +231,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -646,7 +646,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>关系图｜所有过滤方向均为维度→事实单向</x:v>
+        <x:v>关系图｜默认维度→事实单向；DB06日期↔周期状态为双向</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1213,10 +1213,10 @@
         <x:v>1:1</x:v>
       </x:c>
       <x:c r="I17" s="21" t="str">
-        <x:v>维度→事实（单向）</x:v>
+        <x:v>双向</x:v>
       </x:c>
       <x:c r="J17" s="21" t="str">
-        <x:v>拟建</x:v>
+        <x:v>已建并实测PASS</x:v>
       </x:c>
       <x:c r="K17" s="21" t="n">
         <x:v>0</x:v>
